--- a/data/icbanq-ops-requests.xlsx
+++ b/data/icbanq-ops-requests.xlsx
@@ -87,81 +87,203 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>처리자</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>처리일시</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>상세정보</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>REQ-20260630-002</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>수정세금계산서 요청</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>eric@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026.06.30.17:29</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>발행일자변경</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{"업체명":"TEST","기존세금계산서링크":"TGES","수정사항":"발행일자변경","수정이유":"고객사 요청","비고":""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>REQ-20260518-001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>세금계산서 요청</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>아이씨뱅큐</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026.05.18 11:37</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TX-20260518-003 발행 완료</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>전자부품</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>22,000원</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>VIPS팀 처리 완료 샘플</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>

--- a/data/icbanq-ops-requests.xlsx
+++ b/data/icbanq-ops-requests.xlsx
@@ -99,6 +99,11 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>배정담당자</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>상세정보</t>
         </is>
       </c>
@@ -106,27 +111,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REQ-20260630-002</t>
+          <t>REQ-20260706-004</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>수정세금계산서 요청</t>
+          <t>카드결제 확인 요청(등록)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>eric@icbanq.com</t>
+          <t>vincent@icbanq.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026.06.30.17:29</t>
+          <t>2026.07.06.17:38</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -146,12 +151,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>발행일자변경</t>
+          <t>카드 매출전표 확인</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -166,12 +171,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t/>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t/>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -191,97 +196,301 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{"업체명":"TEST","기존세금계산서링크":"TGES","수정사항":"발행일자변경","수정이유":"고객사 요청","비고":""}</t>
+          <t>Vincent, Sally</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>{"업체명":"test","결제금액":"","카드매출전표 업로드":"슬라이드1.JPG"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>REQ-20260706-003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>보증보험 요청</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sally@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026.07.06.17:21</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>undefined ~ undefined</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>15000000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>15,000,000원</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Vincent, Sally</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>{"요청 구분":"나라장터 건","보증보험 종류":"계약이행","업체명":"test","보증요율":"10","보증기간":"undefined ~ undefined","계약명":"test","계약금액(VAT 포함)":"15,000,000원","계약서첨부":"전자(세금)계산서 건별일괄출력 (1).pdf","첨부파일열기구조":"추후 파일 저장소/SharePoint 링크 연결 예정"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260630-002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>수정세금계산서 요청</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>eric@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026.06.30.17:29</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>발행일자변경</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>{"업체명":"TEST","기존세금계산서링크":"TGES","수정사항":"발행일자변경","수정이유":"고객사 요청","비고":""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>REQ-20260518-001</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>세금계산서 요청</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>아이씨뱅큐</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026.05.18 11:37</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TX-20260518-003 발행 완료</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>전자부품</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>22,000원</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>VIPS팀 처리 완료 샘플</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>

--- a/data/icbanq-ops-requests.xlsx
+++ b/data/icbanq-ops-requests.xlsx
@@ -107,16 +107,21 @@
           <t>상세정보</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ERP전송정보</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REQ-20260706-004</t>
+          <t>REQ-20260707-007</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>카드결제 확인 요청(등록)</t>
+          <t>수정세금계산서 요청</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -126,37 +131,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vincent@icbanq.com</t>
+          <t>gavin@icbanq.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026.07.06.17:38</t>
+          <t>2026.07.07.17:05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>요청접수</t>
+          <t>반려</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>요청 반려 처리</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>VIPS팀 접수 대기</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t/>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>카드 매출전표 확인</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -171,49 +176,54 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t/>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t/>
+          <t>-</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VIPS팀</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026.07.07.17:06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Vincent, Sally</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{"업체명":"test","결제금액":"","카드매출전표 업로드":"슬라이드1.JPG"}</t>
+          <t>{"업체명":"test","기존세금계산서링크":"test","수정사항":"1","수정이유":"1"}</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REQ-20260706-003</t>
+          <t>REQ-20260707-006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>보증보험 요청</t>
+          <t>세금계산서 발행 요청</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -228,104 +238,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026.07.06.17:21</t>
+          <t>2026.07.07.15:47</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>요청접수</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>ICBANQ_ERP 전송 완료 (MOCK-ERP-20260707-006)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>VIPS팀 접수 대기</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>VIPS팀 접수 대기</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>undefined ~ undefined</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>15000000</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>15,000,000원</t>
+          <t/>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VIPS팀</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026.07.07.15:47</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Vincent, Sally</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{"요청 구분":"나라장터 건","보증보험 종류":"계약이행","업체명":"test","보증요율":"10","보증기간":"undefined ~ undefined","계약명":"test","계약금액(VAT 포함)":"15,000,000원","계약서첨부":"전자(세금)계산서 건별일괄출력 (1).pdf","첨부파일열기구조":"추후 파일 저장소/SharePoint 링크 연결 예정"}</t>
+          <t>{"업체명":"test","발행일자":"2026-06-30","품목명":"PCB","수량":"1","단가":"1원","공급가액":"","부가세액":"","합계액":"","트래킹 매칭 여부":"매칭 불필요"}</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>{"status":"mock_sent","system":"ICBANQ_ERP","mode":"mock","transmittedAt":"2026.07.07.15:47","transmittedBy":"VIPS팀","externalId":"MOCK-ERP-20260707-006","message":"Mock ERP 전송 완료. 실제 ERP API URL/인증키 연결 시 같은 payload로 전송됩니다.","payload":{"requestId":"REQ-20260707-006","requestType":"taxInvoice","companyName":"test","contactEmail":"VIPS팀 접수 대기","issueDate":"2026-06-30","itemName":"PCB","quantity":1,"unitPrice":1,"supplyAmount":null,"vatAmount":0,"totalAmount":0,"trackingMatchStatus":"매칭 불필요","trackingNumber":"","trackingMemo":"","note":"1","requestedBy":"sally@icbanq.com"}}</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REQ-20260630-002</t>
+          <t>REQ-20260707-005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수정세금계산서 요청</t>
+          <t>입금확인 요청(등록)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TEST</t>
+          <t>test</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>eric@icbanq.com</t>
+          <t>sally@icbanq.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026.06.30.17:29</t>
+          <t>2026.07.07.15:43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -340,17 +355,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t/>
+          <t>VIPS팀 접수 대기</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>발행일자변경</t>
+          <t>입금자: undefined</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -365,17 +380,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1원</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t/>
+          <t>-</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -390,107 +405,423 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sally</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{"업체명":"TEST","기존세금계산서링크":"TGES","수정사항":"발행일자변경","수정이유":"고객사 요청","비고":""}</t>
+          <t>{"업체명":"test","입금일자":"2026-07-16","입금계좌":"우리은행145961","입금금액":"1원"}</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>{}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>REQ-20260706-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>카드결제 확인 요청(등록)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vincent@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026.07.06.17:38</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>카드 매출전표 확인</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>카드 매출전표 확인</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Vincent, Sally</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>{"업체명":"test","결제금액":"","카드매출전표 업로드":"슬라이드1.JPG"}</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20260706-003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>보증보험 요청</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sally@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026.07.06.17:21</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>undefined ~ undefined</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>15000000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>15,000,000원</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Vincent, Sally</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>{"요청 구분":"나라장터 건","보증보험 종류":"계약이행","업체명":"test","보증요율":"10","보증기간":"undefined ~ undefined","계약명":"test","계약금액(VAT 포함)":"15,000,000원","계약서첨부":"전자(세금)계산서 건별일괄출력 (1).pdf","첨부파일열기구조":"추후 파일 저장소/SharePoint 링크 연결 예정"}</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20260630-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>수정세금계산서 요청</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>eric@icbanq.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026.06.30.17:29</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>요청접수</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VIPS팀 접수 대기</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>발행일자변경</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>{"업체명":"TEST","기존세금계산서링크":"TGES","수정사항":"발행일자변경","수정이유":"고객사 요청","비고":""}</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>REQ-20260518-001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>세금계산서 요청</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>아이씨뱅큐</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026.05.18 11:37</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>TX-20260518-003 발행 완료</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>sally@icbanq.com</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>전자부품</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>20000</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>22,000원</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>VIPS팀 처리 완료 샘플</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
